--- a/output/pdf_financials_xlsx/PGX.xlsx
+++ b/output/pdf_financials_xlsx/PGX.xlsx
@@ -6078,49 +6078,49 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.066523</v>
+        <v>0.089173</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.066523</v>
+        <v>0.089173</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.074701</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.204335</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.725451</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.937746</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.130885</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.730659</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.807307</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.067472</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.505387</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.3217</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.885642</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.965222</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.12697</v>
       </c>
     </row>
     <row r="93">
@@ -10059,7 +10059,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12502,7 +12506,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12696,7 +12704,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14165,7 +14177,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -33773,10 +33789,10 @@
         </is>
       </c>
       <c r="S256" s="5" t="n">
-        <v>2.417955</v>
+        <v>-2.417955</v>
       </c>
       <c r="T256" s="5" t="n">
-        <v>1.64596</v>
+        <v>-1.64596</v>
       </c>
       <c r="U256" t="inlineStr">
         <is>
@@ -36371,13 +36387,13 @@
         </is>
       </c>
       <c r="Q282" s="5" t="n">
-        <v>8.673393000000001</v>
+        <v>-8.673393000000001</v>
       </c>
       <c r="R282" s="5" t="n">
-        <v>5.523828</v>
+        <v>-5.523828</v>
       </c>
       <c r="S282" s="5" t="n">
-        <v>2.417955</v>
+        <v>-2.417955</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -39433,19 +39449,19 @@
         </is>
       </c>
       <c r="L313" s="5" t="n">
-        <v>0.17102</v>
+        <v>-0.17102</v>
       </c>
       <c r="M313" s="5" t="n">
-        <v>1.900605</v>
+        <v>-1.900605</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>2.833375</v>
+        <v>-2.833375</v>
       </c>
       <c r="O313" s="5" t="n">
-        <v>1.286592</v>
+        <v>-1.286592</v>
       </c>
       <c r="P313" s="5" t="n">
-        <v>0.981643</v>
+        <v>-0.981643</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -45597,13 +45613,13 @@
         </is>
       </c>
       <c r="J375" s="5" t="n">
-        <v>2.412426</v>
+        <v>-2.412426</v>
       </c>
       <c r="K375" s="5" t="n">
-        <v>4.096775</v>
+        <v>-4.096775</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>0.17102</v>
+        <v>-0.17102</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PGX.xlsx
+++ b/output/pdf_financials_xlsx/PGX.xlsx
@@ -1114,37 +1114,37 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008997</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002522</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001035</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00109</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002332</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003888</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016347</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005681</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02556</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009142000000000001</v>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2150,37 +2150,37 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.412426</v>
+        <v>2.421726</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.184275</v>
+        <v>4.193272</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.17102</v>
+        <v>0.173542</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.900605</v>
+        <v>-1.89957</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.833375</v>
+        <v>-2.832285</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.286592</v>
+        <v>-1.28426</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.286592</v>
+        <v>-1.282704</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-8.673393000000001</v>
+        <v>-8.657045999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.523828</v>
+        <v>-5.518147</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.417955</v>
+        <v>-2.392395</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.417955</v>
+        <v>-2.408813</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2282,37 +2282,37 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.412426</v>
+        <v>2.421726</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.184275</v>
+        <v>4.193272</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.17102</v>
+        <v>0.173542</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.900605</v>
+        <v>-1.89957</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.833375</v>
+        <v>-2.832285</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.286592</v>
+        <v>-1.28426</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.286592</v>
+        <v>-1.282704</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-8.673393000000001</v>
+        <v>-8.657045999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.523828</v>
+        <v>-5.518147</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.417955</v>
+        <v>-2.392395</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.417955</v>
+        <v>-2.408813</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2584,40 +2584,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.194834</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.110779</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.04478</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.059869</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.42031</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.661538</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.495863</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.317479</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.28091</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.229728</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.02979</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.525616</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>3.636299</v>
@@ -2626,13 +2626,13 @@
         <v>0.224796</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.155667</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.476515</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.161105</v>
       </c>
     </row>
     <row r="35">
@@ -2700,40 +2700,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.194834</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.110779</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.04478</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.059869</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.42031</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.661538</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.495863</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.317479</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.28091</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.229728</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.02979</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.525616</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>3.649299</v>
@@ -2742,13 +2742,13 @@
         <v>0.490741</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.033435</v>
+        <v>0.189102</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.011353</v>
+        <v>0.487868</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.001722</v>
+        <v>0.162827</v>
       </c>
     </row>
     <row r="37">
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.194983</v>
+        <v>0.000149</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.110976</v>
+        <v>0.000197</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.0669</v>
+        <v>0.02212</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.050515</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.421143</v>
+        <v>0.000833</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.775259</v>
+        <v>0.113721</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.6019060000000001</v>
+        <v>0.106043</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.370918</v>
+        <v>0.053439</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.488241</v>
+        <v>0.207331</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.332165</v>
+        <v>0.102437</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.061351</v>
+        <v>0.031561</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.5446800000000001</v>
+        <v>0.019064</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.319393</v>
@@ -3438,13 +3438,13 @@
         <v>0.111573</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.212426</v>
+        <v>0.056759</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.592974</v>
+        <v>0.116459</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.220896</v>
+        <v>0.059791</v>
       </c>
     </row>
     <row r="49">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9329,7 +9329,11 @@
           <t>Reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10419,7 +10423,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10922,7 +10926,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -13674,7 +13682,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -14482,7 +14490,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -17691,7 +17699,11 @@
           <t>Purchase of reclamation deposit</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -26094,7 +26106,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -39014,7 +39030,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -45081,7 +45097,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">

--- a/output/pdf_financials_xlsx/PGX.xlsx
+++ b/output/pdf_financials_xlsx/PGX.xlsx
@@ -1408,7 +1408,7 @@
         <v>-2.417955</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.417955</v>
+        <v>-2.485955</v>
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>-4.824852</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-8.28105</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0.34204</v>
@@ -1474,7 +1474,7 @@
         <v>-0</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>0.068</v>
       </c>
       <c r="R17" s="1" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>-2.392395</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.408813</v>
+        <v>-2.476813</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>-2.392395</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.408813</v>
+        <v>-2.476813</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>197.9088372537656</v>
+        <v>2.091162746234414</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>200</v>
@@ -2470,7 +2470,7 @@
         <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.735367293454628</v>
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
@@ -4384,13 +4384,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.035678</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.103033</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.000795</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -4558,13 +4558,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.033479</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.096789</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -7151,16 +7151,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005869</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006709</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039451</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013513</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -7175,13 +7175,13 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001129</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001193</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003318</v>
       </c>
     </row>
     <row r="112">
@@ -7404,16 +7404,16 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.098838</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>9.1e-05</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.073851</v>
       </c>
     </row>
     <row r="116">
@@ -8541,16 +8541,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005869</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006709</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039451</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013513</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8565,13 +8565,13 @@
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001129</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001193</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003318</v>
       </c>
     </row>
     <row r="135">
@@ -8609,7 +8609,7 @@
         <v>-2.06848</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-3.868873</v>
+        <v>-3.874742</v>
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.683969</v>
+        <v>-1.72342</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-2.480976</v>
+        <v>-2.494489</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.566024</v>
@@ -8635,13 +8635,13 @@
         <v>-3.754841</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-1.545419</v>
+        <v>-1.546548</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-1.833305</v>
+        <v>-1.834498</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-1.538315</v>
+        <v>-1.541633</v>
       </c>
     </row>
   </sheetData>
@@ -17600,7 +17600,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -17804,7 +17808,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -20524,7 +20532,11 @@
           <t>Proceed on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -20823,7 +20835,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -21330,7 +21346,11 @@
           <t>Fair value of broker warrants for private placement $</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -22134,7 +22154,11 @@
           <t>Fair value of broker warrants for private placement $</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -24827,7 +24851,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -26005,7 +26033,11 @@
           <t>Deferred income taxes recovery</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -26815,7 +26847,11 @@
           <t>Deferred income taxes recovery</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -33628,7 +33664,11 @@
           <t>Income tax recovery 10</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -45497,7 +45537,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
